--- a/outputs/alternative_b_few_shot.xlsx
+++ b/outputs/alternative_b_few_shot.xlsx
@@ -477,12 +477,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Life-saving antidepressant with no significant side effects despite initial concerns.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -510,12 +510,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Asacol effective in managing Crohn's disease symptoms with no side effects.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Rapid symptom relief</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Contrave helps control overeating and aids weight loss with immediate results.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -609,12 +609,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Effective birth control with minimal side effects, easy cycle regulation.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>No adverse reactions after 2 weeks of use on sensitive areas.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -675,12 +675,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Copper coil causes prolonged pain and heavy periods despite initial benefits.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -708,12 +708,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Effective for headaches, some daytime sleepiness remains</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Methadone withdrawal symptoms worsening despite dose reduction</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication caused mood swings, dryness, and worsening skin issues</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Terrible experience with poor customer support and withdrawal issues.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Minor side effects but effective for some users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Failed to curb appetite or induce feelings of fullness</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>No issues with medication</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Sleep aid helps under extreme stress but may lead to rebound issues.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Provigil improved sleep but had limitations</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Great product helped user quit smoking after just one week.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Birth control caused severe acne, mood swings, and irregular periods.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication helped with sleep and anxiety but lost effectiveness over time.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Quickly relieved symptoms after single dose</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Least effective sleep medication tried in 15 years with mixed results.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Best treatment for IBS-D, improved quality of life significantly.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Severe sensory sensitivity and hallucinations after taking the medication.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>No effect on dry eyes</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>95% sweat-free after 3 days with some side effects</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication misuse leads to poor treatment for Bipolar 2 patients.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Life-restoring medication gave user their life back</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Quickly worked with nail trimming technique for optimal results.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Effective long-term treatment improved sleep quality without side effects.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Significant improvement in bipolar II disorder symptoms with added sertraline</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Life-changing drug eliminated all symptoms with no side-effects.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Rosacea treatment improved significantly with Soolantra, great value for money.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Not too bad despite initial taste issues with no side effects.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Opioid blocker causes withdrawal, nausea, and chills with no pain relief.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Pain relief not reported</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Actos caused significant weight gain and water retention despite dosage reduction.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Cymbalta provides significant relief from chronic pain with manageable side effects.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Fabulous benefits including weight loss and increased libido after stopping birth control.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Transformed my life after group therapy, weight loss, and improved mood.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Egrifta failed to reduce abdominal fat with painful side effects.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Cravings disappeared quickly after starting Campral, reduced drinking desire.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Gabapentin improved impulse control and depression at higher doses</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Plan B One Step effective in preventing pregnancy with side effects.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1897,12 +1897,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Birth control causes severe side effects including acne, mood changes, and vaginal issues.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Pill caused irregular period with heavy cramps and diarrhea</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Effective alternative to oral contraceptive pills with minimal side effects.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Microgestin caused severe side effects including bloating, nausea and heavy painful periods.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Beyond beneficial with improved reading comprehension and focus despite side effects.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Drug works as expected</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication dried out face but failed to prevent new acne and caused skin discoloration</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Birth control caused severe anxiety, depression, and pregnancy-like symptoms</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Severe burning and irritation after using Monistat cream</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Antibiotic caused severe side effects including vaginal discharge and sickness.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Nexplanon causes emotional instability and irregular periods with severe cramps.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Improved acne with reduced severity and faster resolution.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Flomax reduced nocturia but caused dizziness, blurred vision, and fatigue.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Improved pain but experienced side effects including stomach upset and hair loss.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Cryselle effective for endometriosis but causes severe emotional side effects</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Adderall works well initially but loses effectiveness over time</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Benzol peroxide and Retin-A improved acne significantly with increased confidence.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Med caused significant side effects including bladder control loss and memory issues.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Procedure was relatively painless with minimal discomfort afterwards.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2527,12 +2527,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Severe allergic reaction with swelling and watery eyes, extremely expensive.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication triggered severe anxiety attack, withdrawal symptoms, and intense physical reactions.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Rare side effects including palpitations and dizziness occurred after 4 hours.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication helps with energy and calmness but causes mental thoughts</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Afrezza mimics healthy pancreas, manages glucose in real-time quickly.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Zoloft worsened depression with extreme weight gain and fatigue.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2725,12 +2725,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Effective in eliminating auditory hallucinations completely</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Severe allergic reaction to Bactrim led to ICU stay and prolonged hospitalization.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Blisovi causes skin breakouts and weight gain, not recommended.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Zoloft helped me overcome major depression and regain my life.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Life-changing antiperspirant cured hyperhidrosis completely but caused severe burns.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Severe anxiety, nausea, tinnitus, and extreme fatigue after 10 hours.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>IUD caused severe cramping, heavy periods, and intense pain leading removal.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2956,12 +2956,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Miraculous transformation from severe anxiety to well-being with Lyrica.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Birth control alters menstrual cycle with nausea and depression</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Ultram relieves severe pelvic pain and adhesions with significant improvement.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3056,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Weight loss with reduced hunger</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Life-changing drug eliminated all chronic symptoms quickly with no side-effects.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Life-changing antidepressant with minimal side effects improved sleep and mental clarity.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Severe side effects including intense numbness, nausea, and seizures</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Plan B pill alleviated symptoms but caused heavy bleeding and cramps.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication caused dizziness and lightheadedness with uncertain anxiety benefits.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Beneficial when combined with muscle relaxer for severe pain relief.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>No side effects after two weeks on medication</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3320,12 +3320,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication effective but generic version causes financial burden</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Effective for uncontrolled nausea and vomiting, puts patient to sleep.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Skin cream causes intense itching and burning with some relief</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Knee condition worsened significantly after medication, causing severe pain.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Implant failed to regulate periods, now experiencing spotting issues.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Effective for motion sickness with good results and user recommendation.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Excellent experience with reduced bleeding and minimal side effects over time.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Helpful for bipolar disorder, but monitor body response closely.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medicine causes severe fluid buildup and uncontrolled blood pressure</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Medication helps with psoriasis and PSA, but has short duration</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3651,12 +3651,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Drug caused severe side effects</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Vicodin effective but habit-forming with tolerance over time</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Helps alleviate general discomfort and pain after sitting</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>API Execution Error</t>
+          <t>Procedure was a waste of energy, but minor cramping manageable</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
